--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -124,7 +124,7 @@
     <t xml:space="preserve">Optoacoplador PC817</t>
   </si>
   <si>
-    <t xml:space="preserve">Detecta el uso manual de cada botón, aislando los 24 V AC</t>
+    <t xml:space="preserve">Detecta el uso manual de cada botón, aislando la tensión de la botonera</t>
   </si>
   <si>
     <t xml:space="preserve">pin1←R 2,2k · pin2←DB157(−) · pin3→GND · pin4→GPIO</t>
@@ -136,7 +136,7 @@
     <t xml:space="preserve">Puente rectificador DB157 </t>
   </si>
   <si>
-    <t xml:space="preserve">Convierte el 24 V AC del botón en continua</t>
+    <t xml:space="preserve">Convierte la tensión del botón en continua (si ya fuera continua, la deja pasar igual)</t>
   </si>
   <si>
     <t xml:space="preserve">~ y ~ al par del botón · + a la R · − al pin 2</t>
@@ -166,7 +166,7 @@
     <t xml:space="preserve">Entre DB157(+) y pin 1 del PC817</t>
   </si>
   <si>
-    <t xml:space="preserve">1 W: con 24 V disipa calor, no usar de 1/4 W.</t>
+    <t xml:space="preserve">1 W: con 24 V disipa calor, no usar de 1/4 W. Si la botonera midiera entre 12 y 18 V, va de 1,2 kΩ. Si la botonera midiera entre 12 y 18 V, va de 1,2 kΩ.</t>
   </si>
   <si>
     <t xml:space="preserve">── COMPONENTES PASIVOS ──</t>

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>Las 2 patas AC a la red (sin polaridad) · +Vo y −Vo al bus de 5 V</t>
+          <t>Soldado en su propia plaqueta: bornera de 220 V a las 2 patas AC (sin polaridad) · +Vo y −Vo a la bornera de 5 V, que va a la placa principal</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
@@ -862,11 +862,11 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard)</t>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>La entrega final va soldada, no sobre protoboard.</t>
+          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión.</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Fijan la placa y los módulos al fondo del gabinete</t>
+          <t>Fijan las placas y los módulos de relé al fondo del gabinete</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="6" min="1" max="1"/>
@@ -840,53 +840,53 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="7">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>── MONTAJE Y CONEXIONADO ──</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
+    <row r="18" ht="30" customHeight="1" s="7">
+      <c r="A18" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Capacitor electrolítico 470 µF (220 a 470 µF) 16 V o más</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Sostiene el bus de 5 V cuando engancha un relé mientras el ESP32 transmite por WiFi</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Entre 5 V y GND, junto a la entrada del bus en la placa principal</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>TIENE POLARIDAD: pata larga (o el lado sin franja) al +5 V. Es el capacitor de 470 µF del diagrama del Bloque A.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="7">
-      <c r="A19" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Placa universal perforada</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="7">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>── ETAPA 4 · NIVEL 2 (Bloques C y D: se suman a la placa principal al armarlos) ──</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="7">
       <c r="A20" s="10" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Gabinete IP65 + prensacables</t>
+          <t>Optoacoplador PC817 (sensor de pasada)</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
@@ -894,17 +894,17 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Protege el nodo del polvo y la pelusa textil</t>
+          <t>Aísla la señal del sensor inductivo del GPIO 35</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>pin1←R 1,2k←positivo del telar · pin2→negro del sensor · pin3→GND · pin4→GPIO 35</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Montado en pared o columna, no sobre el chasis del telar.</t>
+          <t>El azul del sensor va al negativo del telar, nunca al GND del ESP32.</t>
         </is>
       </c>
     </row>
@@ -914,79 +914,287 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Borneras de tornillo</t>
+          <t>Resistencia 1,2 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Conexión de los cables que entran y salen del gabinete</t>
+          <t>Limita la corriente del LED del PC817 (unos 10 mA con 12 a 14 V)</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Red, bus de 5 V y los 3 pares del telar</t>
+          <t>Entre el positivo del telar y el pin 1 del PC817</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>Permiten desconectar sin desoldar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="53.25" customHeight="1" s="7">
+          <t>Si la tensión medida diera 24 V, va de 2,2 kΩ 1/2 W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="7">
       <c r="A22" s="10" t="n">
         <v>16</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Cable multifilar 6 conductores, 1 mm²</t>
+          <t>Resistencia 10 kΩ 1/4 W (sensor)</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Lleva la señal de los 3 botones hasta el gabinete: el mismo par sirve para el relé y para el sensado</t>
+          <t>Pull-up del GPIO 35 (no tiene resistencia interna)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Un par por botón, del telar a las borneras del gabinete</t>
+          <t>Entre GPIO 35 y 3V3</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Sin blindaje. Se descartó el cable mallado tras consulta profesional: la señal de contacto seco a 24 V tiene inmunidad de sobra, el telar no tiene variador de frecuencia y su electrónica está en una caja metálica que contiene el ruido. Único recaudo: no correrlo pegado y en paralelo al cable del motor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="21.75" customHeight="1" s="7">
+          <t>Obligatoria: sin ella el pin queda al aire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="7">
       <c r="A23" s="10" t="n">
         <v>17</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
+          <t>Relé OptoMOS LCA110 (DIP-6)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Corta la señal de cada lector óptico (uno por bobina de selección)</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>pin1←R 330 Ω←GPIO 18/19/21/22 · pin2→GND · pin4 y pin6 al lector (serie o paralelo) · pin3 y 5 sin conectar</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>La salida (4 y 6) queda aislada del ESP32: nunca unir sus cables con el GND del ESP32.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="7">
+      <c r="A24" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Resistencia 330 Ω 1/4 W</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Limita la corriente del LED de cada LCA110 (unos 6 mA)</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Entre cada GPIO (18, 19, 21, 22) y el pin 1 de su LCA110</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>No es opcional: sin ella se daña el LED del relé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="7">
+      <c r="A25" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Resistencia 10 kΩ 1/4 W (canales)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Arranque seguro de los canales de selección</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Entre cada GPIO (18, 19, 21, 22) y GND</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>A GND, no a 3V3: el LCA110 conduce con el pin en alto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="7">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>── MONTAJE Y CONEXIONADO ──</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="7">
+      <c r="A27" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Placa universal perforada</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="7">
+      <c r="A28" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Gabinete IP65 + prensacables</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Protege el nodo del polvo y la pelusa textil</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Montado en pared o columna, no sobre el chasis del telar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="7">
+      <c r="A29" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Borneras de tornillo</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Conexión de los cables que entran y salen del gabinete</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Red, bus de 5 V y los 3 pares del telar</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Permiten desconectar sin desoldar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="53.25" customHeight="1" s="7">
+      <c r="A30" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Cable multifilar 6 conductores, 1 mm²</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Lleva la señal de los 3 botones hasta el gabinete: el mismo par sirve para el relé y para el sensado</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Un par por botón, del telar a las borneras del gabinete</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Sin blindaje. Se descartó el cable mallado tras consulta profesional: la señal de contacto seco a 24 V tiene inmunidad de sobra, el telar no tiene variador de frecuencia y su electrónica está en una caja metálica que contiene el ruido. Único recaudo: no correrlo pegado y en paralelo al cable del motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="21.75" customHeight="1" s="7">
+      <c r="A31" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
           <t>Separadores / standoffs + tornillos</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Fijan las placas y los módulos de relé al fondo del gabinete</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Etapa provisoria con cinta doble faz; el montaje definitivo va con separadores.</t>
         </is>

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="6" min="1" max="1"/>
@@ -1070,11 +1070,11 @@
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente</t>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -1197,6 +1197,34 @@
       <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Etapa provisoria con cinta doble faz; el montaje definitivo va con separadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="7">
+      <c r="A32" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Tiras de pines (2x, 5x, 6x y 8x)</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Conectores enchufables en la plaqueta para el ESP32, los módulos y los cables</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>19 tiras de 2 pines · 6 de 5 · 4 de 6 · 2 de 8</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Se suman el 10/10/2026. Permiten sacar módulos y cables sin desoldar.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes en placa" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Componentes en placa'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -125,7 +127,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -159,6 +161,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -411,9 +416,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="6" min="1" max="1"/>
@@ -458,7 +463,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" s="7">
       <c r="A2" s="9" t="n"/>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>── ETAPA 1 · ALIMENTACIÓN (220 V) ──</t>
         </is>
@@ -468,7 +473,7 @@
       <c r="E2" s="9" t="n"/>
       <c r="F2" s="9" t="n"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="7">
+    <row r="3" ht="37.5" customHeight="1" s="7">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
@@ -554,7 +559,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" s="7">
       <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>── ETAPA 2 · CONTROL (salidas a la botonera) ──</t>
         </is>
@@ -650,7 +655,7 @@
     </row>
     <row r="10" ht="15" customHeight="1" s="7">
       <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>── ETAPA 3 · SENSADO (lectura de la botonera) ──</t>
         </is>
@@ -660,7 +665,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="7">
+    <row r="11" ht="26" customHeight="1" s="7">
       <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
@@ -688,7 +693,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="7">
+    <row r="12" ht="26" customHeight="1" s="7">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -716,7 +721,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="63.75" customHeight="1" s="7">
+    <row r="13" ht="72" customHeight="1" s="7">
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
@@ -744,7 +749,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="7">
+    <row r="14" ht="26" customHeight="1" s="7">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -774,7 +779,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" s="7">
       <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>── COMPONENTES PASIVOS ──</t>
         </is>
@@ -840,7 +845,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="7">
+    <row r="18" ht="26" customHeight="1" s="7">
       <c r="A18" s="10" t="n">
         <v>13</v>
       </c>
@@ -870,7 +875,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" s="7">
       <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>── ETAPA 4 · NIVEL 2 (Bloques C y D: se suman a la placa principal al armarlos) ──</t>
         </is>
@@ -880,7 +885,7 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="7">
+    <row r="20" ht="26" customHeight="1" s="7">
       <c r="A20" s="10" t="n">
         <v>14</v>
       </c>
@@ -908,7 +913,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="7">
+    <row r="21" ht="26" customHeight="1" s="7">
       <c r="A21" s="10" t="n">
         <v>15</v>
       </c>
@@ -964,7 +969,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="7">
+    <row r="23" ht="37.5" customHeight="1" s="7">
       <c r="A23" s="10" t="n">
         <v>17</v>
       </c>
@@ -978,21 +983,21 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Corta la señal de cada lector óptico (uno por bobina de selección)</t>
+          <t>Da la señal en lugar de cada lector óptico (uno por bobina de selección)</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>pin1←R 330 Ω←GPIO 18/19/21/22 · pin2→GND · pin4 y pin6 al lector (serie o paralelo) · pin3 y 5 sin conectar</t>
+          <t>pin1←R 330 Ω←GPIO 18/19/21/22 · pin2→GND · pin4←R de protección←+ del conector del lector · pin6→señal del lector · pin3 y 5 sin conectar</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>La salida (4 y 6) queda aislada del ESP32: nunca unir sus cables con el GND del ESP32.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="7">
+          <t>La salida (4 y 6) queda aislada del ESP32: nunca unir sus cables con el GND del ESP32. Conexión final: diagramas/hardware/conexion_final_rele.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1" s="7">
       <c r="A24" s="10" t="n">
         <v>18</v>
       </c>
@@ -1049,24 +1054,40 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="7">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>── MONTAJE Y CONEXIONADO ──</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="7">
+      <c r="A26" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Zócalo DIP de 6 patas</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Permite cambiar un LCA110 sin desoldar</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Soldado en la placa; el relé va enchufado</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>La muesca del zócalo y la del relé, del lado de la pata 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1" s="7">
       <c r="A27" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Placa universal perforada</t>
+          <t>Resistencia de protección (220 Ω 2 W o 470 Ω 3 W)</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
@@ -1074,111 +1095,95 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta</t>
+          <t>Lado del telar: limita la corriente si hay un error de cableado</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Entre el + del conector de cada lector y el pin 4 de su LCA110</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión.</t>
+          <t>220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V. Del lado del telar: nunca al GND del ESP32.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="7">
       <c r="A28" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gabinete IP65 + prensacables</t>
+          <t>Resistencia 10 kΩ 1/2 W (lado del telar)</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Protege el nodo del polvo y la pelusa textil</t>
+          <t>Deja la señal en 0 V (papel) con el relé abierto</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Entre la señal y el − del conector de cada lector</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Montado en pared o columna, no sobre el chasis del telar.</t>
+          <t>Del lado del telar: nunca al GND del ESP32.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="7">
-      <c r="A29" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Borneras de tornillo</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Conexión de los cables que entran y salen del gabinete</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Red, bus de 5 V y los 3 pares del telar</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>Permiten desconectar sin desoldar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="53.25" customHeight="1" s="7">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>── MONTAJE Y CONEXIONADO ──</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1" s="7">
       <c r="A30" s="10" t="n">
         <v>23</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Cable multifilar 6 conductores, 1 mm²</t>
+          <t>Placa universal perforada</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Lleva la señal de los 3 botones hasta el gabinete: el mismo par sirve para el relé y para el sensado</t>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Un par por botón, del telar a las borneras del gabinete</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Sin blindaje. Se descartó el cable mallado tras consulta profesional: la señal de contacto seco a 24 V tiene inmunidad de sobra, el telar no tiene variador de frecuencia y su electrónica está en una caja metálica que contiene el ruido. Único recaudo: no correrlo pegado y en paralelo al cable del motor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="21.75" customHeight="1" s="7">
+          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="7">
       <c r="A31" s="10" t="n">
         <v>24</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Separadores / standoffs + tornillos</t>
+          <t>Gabinete IP65 + prensacables</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
@@ -1186,7 +1191,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Fijan las placas y los módulos de relé al fondo del gabinete</t>
+          <t>Protege el nodo del polvo y la pelusa textil</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -1196,33 +1201,117 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Etapa provisoria con cinta doble faz; el montaje definitivo va con separadores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="7">
+          <t>Montado en pared o columna, no sobre el chasis del telar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="37.5" customHeight="1" s="7">
       <c r="A32" s="10" t="n">
         <v>25</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
+          <t>Borneras de tornillo</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Conexión de los cables que entran y salen del gabinete</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Red, bus de 5 V y los 3 pares del telar</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Permiten desconectar sin desoldar. El Bloque D suma 8 borneras de 4 vías en el lado del telar (dos por canal, en el conector del lector).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60.5" customHeight="1" s="7">
+      <c r="A33" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Cable multifilar 6 conductores, 1 mm²</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Lleva la señal de los 3 botones hasta el gabinete: el mismo par sirve para el relé y para el sensado</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Un par por botón, del telar a las borneras del gabinete</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Sin blindaje. Se descartó el cable mallado tras consulta profesional: la señal de contacto seco a 24 V tiene inmunidad de sobra, el telar no tiene variador de frecuencia y su electrónica está en una caja metálica que contiene el ruido. Único recaudo: no correrlo pegado y en paralelo al cable del motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1" s="7">
+      <c r="A34" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Separadores / standoffs + tornillos</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Fijan las placas y los módulos de relé al fondo del gabinete</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Etapa provisoria con cinta doble faz; el montaje definitivo va con separadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1" s="7">
+      <c r="A35" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
           <t>Tiras de pines (2x, 5x, 6x y 8x)</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C35" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Conectores enchufables en la plaqueta para el ESP32, los módulos y los cables</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>19 tiras de 2 pines · 6 de 5 · 4 de 6 · 2 de 8</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Se suman el 10/10/2026. Permiten sacar módulos y cables sin desoldar.</t>
         </is>
@@ -1231,6 +1320,6 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes en placa" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Componentes en placa'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -125,7 +127,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -159,6 +161,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -411,9 +416,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="6" min="1" max="1"/>
@@ -458,7 +463,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" s="7">
       <c r="A2" s="9" t="n"/>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>── ETAPA 1 · ALIMENTACIÓN (220 V) ──</t>
         </is>
@@ -468,7 +473,7 @@
       <c r="E2" s="9" t="n"/>
       <c r="F2" s="9" t="n"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="7">
+    <row r="3" ht="37.5" customHeight="1" s="7">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
@@ -554,7 +559,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" s="7">
       <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>── ETAPA 2 · CONTROL (salidas a la botonera) ──</t>
         </is>
@@ -650,7 +655,7 @@
     </row>
     <row r="10" ht="15" customHeight="1" s="7">
       <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>── ETAPA 3 · SENSADO (lectura de la botonera) ──</t>
         </is>
@@ -660,7 +665,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="7">
+    <row r="11" ht="26" customHeight="1" s="7">
       <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
@@ -688,7 +693,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="7">
+    <row r="12" ht="26" customHeight="1" s="7">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -716,7 +721,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="63.75" customHeight="1" s="7">
+    <row r="13" ht="72" customHeight="1" s="7">
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
@@ -744,7 +749,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="7">
+    <row r="14" ht="26" customHeight="1" s="7">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -774,7 +779,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" s="7">
       <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>── COMPONENTES PASIVOS ──</t>
         </is>
@@ -840,7 +845,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="7">
+    <row r="18" ht="26" customHeight="1" s="7">
       <c r="A18" s="10" t="n">
         <v>13</v>
       </c>
@@ -870,7 +875,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" s="7">
       <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>── ETAPA 4 · NIVEL 2 (Bloques C y D: se suman a la placa principal al armarlos) ──</t>
         </is>
@@ -880,7 +885,7 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="7">
+    <row r="20" ht="26" customHeight="1" s="7">
       <c r="A20" s="10" t="n">
         <v>14</v>
       </c>
@@ -908,7 +913,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="7">
+    <row r="21" ht="26" customHeight="1" s="7">
       <c r="A21" s="10" t="n">
         <v>15</v>
       </c>
@@ -964,7 +969,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="7">
+    <row r="23" ht="37.5" customHeight="1" s="7">
       <c r="A23" s="10" t="n">
         <v>17</v>
       </c>
@@ -978,21 +983,21 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Corta la señal de cada lector óptico (uno por bobina de selección)</t>
+          <t>Da la señal en lugar de cada lector óptico (uno por bobina de selección)</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>pin1←R 330 Ω←GPIO 18/19/21/22 · pin2→GND · pin4 y pin6 al lector (serie o paralelo) · pin3 y 5 sin conectar</t>
+          <t>pin1←R 330 Ω←GPIO 18/19/21/22 · pin2→GND · pin4←R de protección←+ del conector del lector · pin6→señal del lector · pin3 y 5 sin conectar</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>La salida (4 y 6) queda aislada del ESP32: nunca unir sus cables con el GND del ESP32.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="7">
+          <t>La salida (4 y 6) queda aislada del ESP32: nunca unir sus cables con el GND del ESP32. Conexión final: diagramas/hardware/conexion_final_rele.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1" s="7">
       <c r="A24" s="10" t="n">
         <v>18</v>
       </c>
@@ -1049,136 +1054,136 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="7">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>── MONTAJE Y CONEXIONADO ──</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="7">
+      <c r="A26" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Zócalo DIP de 6 patas</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Permite cambiar un LCA110 sin desoldar</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Soldado en la placa; el relé va enchufado</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>La muesca del zócalo y la del relé, del lado de la pata 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1" s="7">
       <c r="A27" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Placa universal perforada</t>
+          <t>Resistencia de protección (220 Ω 2 W o 470 Ω 3 W)</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente</t>
+          <t>Lado del telar: limita la corriente si hay un error de cableado</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Entre el + del conector de cada lector y el pin 4 de su LCA110</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión.</t>
+          <t>220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V. Del lado del telar: nunca al GND del ESP32.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="7">
       <c r="A28" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gabinete IP65 + prensacables</t>
+          <t>Resistencia 10 kΩ 1/2 W (lado del telar)</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Protege el nodo del polvo y la pelusa textil</t>
+          <t>Deja la señal en 0 V (papel) con el relé abierto</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Entre la señal y el − del conector de cada lector</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Montado en pared o columna, no sobre el chasis del telar.</t>
+          <t>Del lado del telar: nunca al GND del ESP32.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="7">
-      <c r="A29" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Borneras de tornillo</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Conexión de los cables que entran y salen del gabinete</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Red, bus de 5 V y los 3 pares del telar</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>Permiten desconectar sin desoldar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="53.25" customHeight="1" s="7">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>── MONTAJE Y CONEXIONADO ──</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1" s="7">
       <c r="A30" s="10" t="n">
         <v>23</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Cable multifilar 6 conductores, 1 mm²</t>
+          <t>Placa universal perforada</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Lleva la señal de los 3 botones hasta el gabinete: el mismo par sirve para el relé y para el sensado</t>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Un par por botón, del telar a las borneras del gabinete</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Sin blindaje. Se descartó el cable mallado tras consulta profesional: la señal de contacto seco a 24 V tiene inmunidad de sobra, el telar no tiene variador de frecuencia y su electrónica está en una caja metálica que contiene el ruido. Único recaudo: no correrlo pegado y en paralelo al cable del motor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="21.75" customHeight="1" s="7">
+          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="7">
       <c r="A31" s="10" t="n">
         <v>24</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Separadores / standoffs + tornillos</t>
+          <t>Gabinete IP65 + prensacables</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
@@ -1186,23 +1191,135 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
+          <t>Protege el nodo del polvo y la pelusa textil</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Montado en pared o columna, no sobre el chasis del telar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="37.5" customHeight="1" s="7">
+      <c r="A32" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Borneras de tornillo</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Conexión de los cables que entran y salen del gabinete</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Red, bus de 5 V y los 3 pares del telar</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Permiten desconectar sin desoldar. El Bloque D suma 8 borneras de 4 vías en el lado del telar (dos por canal, en el conector del lector).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60.5" customHeight="1" s="7">
+      <c r="A33" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Cable multifilar 6 conductores, 1 mm²</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Lleva la señal de los 3 botones hasta el gabinete: el mismo par sirve para el relé y para el sensado</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Un par por botón, del telar a las borneras del gabinete</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Sin blindaje. Se descartó el cable mallado tras consulta profesional: la señal de contacto seco a 24 V tiene inmunidad de sobra, el telar no tiene variador de frecuencia y su electrónica está en una caja metálica que contiene el ruido. Único recaudo: no correrlo pegado y en paralelo al cable del motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1" s="7">
+      <c r="A34" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Separadores / standoffs + tornillos</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
           <t>Fijan las placas y los módulos de relé al fondo del gabinete</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Etapa provisoria con cinta doble faz; el montaje definitivo va con separadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1" s="7">
+      <c r="A35" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Tiras de pines (2x, 5x, 6x y 8x)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Conectores enchufables en la plaqueta para el ESP32, los módulos y los cables</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>19 tiras de 2 pines · 6 de 5 · 4 de 6 · 2 de 8</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Se suman el 10/10/2026. Permiten sacar módulos y cables sin desoldar.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -721,13 +721,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1" s="7">
+    <row r="13" ht="88" customHeight="1" s="7">
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Capacitor electrolítico 22–47 µF 50 V</t>
+          <t>Capacitor electrolítico 22 µF 50 V</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Aplana el AC rectificado: sin él, el sensado lee varias pulsaciones donde hubo una sola</t>
+          <t>Mantiene encendido el LED del PC817 entre los semiciclos del rectificado: sin él, el sensado manda avisos solos, sin que nadie apriete nada</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -745,11 +745,11 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>TIENE POLARIDAD: pata larga (o el lado sin franja) al +. Va en paralelo entre + y − del DB157, antes de la resistencia. Sirve cualquier valor entre 22 y 47 µF: el de 22 µF responde algo más rápido al soltar el botón y el de 47 µF filtra mejor; ambos funcionan. Ya instalado 1 de 47 µF en el canal de Retroceder, que es el crítico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1" s="7">
+          <t>TIENE POLARIDAD: pata larga (o el lado sin franja) al +. Va en paralelo entre + y − del DB157, antes de la resistencia. Va de 22 µF en los tres canales: el valor fija cuánto hay que mantener apretado el botón para que se registre (con 22 µF, entre 0,15 y 0,25 s; con 47 µF, entre 0,3 y 0,5 s, y un toque rápido se pierde). En la protoboard quedó uno de 47 µF en el canal de Retroceder: en la plaqueta va de 22 µF, como los otros dos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="7">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -773,7 +773,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>1 W: con 24 V disipa calor, no usar de 1/4 W. Si la botonera midiera entre 12 y 18 V, va de 1,2 kΩ.</t>
+          <t>1 W: con 24 V disipa calor, no usar de 1/4 W. Si la botonera midiera entre 12 y 18 V, va de 1,2 kΩ 1 W.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -1149,7 +1149,7 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="9" t="n"/>
     </row>
-    <row r="30" ht="72" customHeight="1" s="7">
+    <row r="30" ht="88" customHeight="1" s="7">
       <c r="A30" s="10" t="n">
         <v>23</v>
       </c>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta</t>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32 y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta. El sensado de la botonera va en su propia plaqueta impresa (diseñada en Proteus), unida a la principal por J4</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="37.5" customHeight="1" s="7">
+    <row r="32" ht="40" customHeight="1" s="7">
       <c r="A32" s="10" t="n">
         <v>25</v>
       </c>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Red, bus de 5 V y los 3 pares del telar</t>
+          <t>Red, bus de 5 V y B1 en la plaqueta de sensado: dos por botón (el par de la botonera y el par que va a NO y COM de su relé)</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -721,13 +721,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1" s="7">
+    <row r="13" ht="88" customHeight="1" s="7">
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Capacitor electrolítico 22–47 µF 50 V</t>
+          <t>Capacitor electrolítico 22 µF 50 V</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Aplana el AC rectificado: sin él, el sensado lee varias pulsaciones donde hubo una sola</t>
+          <t>Mantiene encendido el LED del PC817 entre los semiciclos del rectificado: sin él, el sensado manda avisos solos, sin que nadie apriete nada</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -745,11 +745,11 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>TIENE POLARIDAD: pata larga (o el lado sin franja) al +. Va en paralelo entre + y − del DB157, antes de la resistencia. Sirve cualquier valor entre 22 y 47 µF: el de 22 µF responde algo más rápido al soltar el botón y el de 47 µF filtra mejor; ambos funcionan. Ya instalado 1 de 47 µF en el canal de Retroceder, que es el crítico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1" s="7">
+          <t>TIENE POLARIDAD: pata larga (o el lado sin franja) al +. Va en paralelo entre + y − del DB157, antes de la resistencia. Va de 22 µF en los tres canales: el valor fija cuánto hay que mantener apretado el botón para que se registre (con 22 µF, entre 0,15 y 0,25 s; con 47 µF, entre 0,3 y 0,5 s, y un toque rápido se pierde). En la protoboard quedó uno de 47 µF en el canal de Retroceder: en la plaqueta va de 22 µF, como los otros dos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="7">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -773,7 +773,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>1 W: con 24 V disipa calor, no usar de 1/4 W. Si la botonera midiera entre 12 y 18 V, va de 1,2 kΩ.</t>
+          <t>1 W: con 24 V disipa calor, no usar de 1/4 W. Si la botonera midiera entre 12 y 18 V, va de 1,2 kΩ 1 W.</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="9" t="n"/>
     </row>
-    <row r="30" ht="72" customHeight="1" s="7">
+    <row r="30" ht="88" customHeight="1" s="7">
       <c r="A30" s="10" t="n">
         <v>23</v>
       </c>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32, sensado y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta</t>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32 y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta. El sensado de la botonera va en su propia plaqueta impresa (diseñada en Proteus), unida a la principal por J4</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="37.5" customHeight="1" s="7">
+    <row r="32" ht="40" customHeight="1" s="7">
       <c r="A32" s="10" t="n">
         <v>25</v>
       </c>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Red, bus de 5 V y los 3 pares del telar</t>
+          <t>Red, bus de 5 V y B1 en la plaqueta de sensado: dos por botón (el par de la botonera y el par que va a NO y COM de su relé)</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -877,7 +877,7 @@
       <c r="A19" s="9" t="n"/>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>── ETAPA 4 · NIVEL 2 (Bloques C y D: se suman a la placa principal al armarlos) ──</t>
+          <t>── ETAPA 4 · NIVEL 2 (Bloques C y D: se suman al armarlos, en su plaqueta unida a la principal por J3) ──</t>
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard): la principal (ESP32 y Bloques C y D), la de los módulos de relé y una chica para la fuente. Se suma una más (10/10/2026): con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta. El sensado de la botonera va en su propia plaqueta impresa (diseñada en Proteus), unida a la principal por J4</t>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la de la fuente, la principal (ESP32), la de los módulos de relé y la del Nivel 2 (Bloques C y D, sumada el 10/10/2026, con todo ya probado en protoboard). El sensado de la botonera va en su propia plaqueta impresa (diseñada en Proteus), unida a la principal por J4</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puente rectificador DB157 </t>
+          <t xml:space="preserve">Puente rectificador DB157</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Resistencia de protección (220 Ω 2 W o 470 Ω 3 W)</t>
+          <t>Resistencia de protección 470 Ω 3 W</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V. Del lado del telar: nunca al GND del ESP32.</t>
+          <t>De 470 Ω 3 W porque el lector del C 201 se alimenta con 15 a 30 V (medido el 17/10/2026); con hasta 15 V sería de 220 Ω 2 W. Del lado del telar: nunca al GND del ESP32.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -127,7 +127,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -164,6 +164,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -473,85 +482,85 @@
       <c r="E2" s="9" t="n"/>
       <c r="F2" s="9" t="n"/>
     </row>
-    <row r="3" ht="37.5" customHeight="1" s="7">
-      <c r="A3" s="10" t="n">
+    <row r="3" ht="47" customHeight="1" s="7">
+      <c r="A3" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Módulo HLK-5M05 (220 V AC → 5 V DC, 1 A)</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Alimenta todo el nodo desde la red, aislado del telar</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Soldado en su propia plaqueta: bornera de 220 V a las 2 patas AC (sin polaridad) · +Vo y −Vo a la bornera de 5 V, que va a la placa principal</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Las patas AC no tienen polaridad. +Vo/−Vo SÍ: invertirlas quema el ESP32.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="7">
-      <c r="A4" s="10" t="n">
+    <row r="4" ht="25" customHeight="1" s="7">
+      <c r="A4" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Fusible 1 A lento + portafusible</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Protege la entrada de red del módulo de fuente</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>En serie con la FASE únicamente</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Nunca en el neutro. Empalmes aislados con termocontraíble.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="7">
-      <c r="A5" s="10" t="n">
+    <row r="5" ht="25" customHeight="1" s="7">
+      <c r="A5" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Cable de alimentación 220 V con ficha</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Conexión a la red de la planta</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Fase → fusible → L · Neutro → N</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Fase marrón, neutro celeste. Sin conectores dupont en este lado.</t>
         </is>
@@ -569,29 +578,29 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="9" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="7">
-      <c r="A7" s="10" t="n">
+    <row r="7" ht="25" customHeight="1" s="7">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>ESP32 NodeMCU-32</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Consulta el estado en el backend y acciona los relés</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>5V/VIN y GND al bus · GPIO según esquema</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Alimentar por el bus de 5 V o por USB, nunca por ambos a la vez.</t>
         </is>
@@ -699,7 +708,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puente rectificador DB157</t>
+          <t>Puente rectificador DB157</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
@@ -721,29 +730,29 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1" s="7">
-      <c r="A13" s="10" t="n">
+    <row r="13" ht="91" customHeight="1" s="7">
+      <c r="A13" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Capacitor electrolítico 22 µF 50 V</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Mantiene encendido el LED del PC817 entre los semiciclos del rectificado: sin él, el sensado manda avisos solos, sin que nadie apriete nada</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>En paralelo a la salida del DB157 (+ y −), antes de la R de 2,2 kΩ</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>TIENE POLARIDAD: pata larga (o el lado sin franja) al +. Va en paralelo entre + y − del DB157, antes de la resistencia. Va de 22 µF en los tres canales: el valor fija cuánto hay que mantener apretado el botón para que se registre (con 22 µF, entre 0,15 y 0,25 s; con 47 µF, entre 0,3 y 0,5 s, y un toque rápido se pierde). En la protoboard quedó uno de 47 µF en el canal de Retroceder: en la plaqueta va de 22 µF, como los otros dos.</t>
         </is>
@@ -789,29 +798,29 @@
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="7">
-      <c r="A16" s="10" t="n">
+    <row r="16" ht="25" customHeight="1" s="7">
+      <c r="A16" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Resistencia 10 kΩ 1/4 W</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Mantienen los pines en nivel seguro al encender</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>3 en los relés + 3 en el sensado</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>5 van a 3V3 y la de GPIO 27 va a GND (módulo activo-alto).</t>
         </is>
@@ -873,9 +882,9 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="7">
+    <row r="19" ht="38" customHeight="1" s="7">
       <c r="A19" s="9" t="n"/>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>── ETAPA 4 · NIVEL 2 (Bloques C y D: se suman al armarlos, en su plaqueta unida a la principal por J3) ──</t>
         </is>
@@ -941,29 +950,29 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="7">
-      <c r="A22" s="10" t="n">
+    <row r="22" ht="25" customHeight="1" s="7">
+      <c r="A22" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Resistencia 10 kΩ 1/4 W (sensor)</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Pull-up del GPIO 35 (no tiene resistencia interna)</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Entre GPIO 35 y 3V3</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Obligatoria: sin ella el pin queda al aire.</t>
         </is>
@@ -1053,85 +1062,85 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="7">
-      <c r="A26" s="10" t="n">
+    <row r="26" ht="25" customHeight="1" s="7">
+      <c r="A26" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Zócalo DIP de 6 patas</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Permite cambiar un LCA110 sin desoldar</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Soldado en la placa; el relé va enchufado</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>La muesca del zócalo y la del relé, del lado de la pata 1.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1" s="7">
-      <c r="A27" s="10" t="n">
+    <row r="27" ht="36" customHeight="1" s="7">
+      <c r="A27" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Resistencia de protección 470 Ω 3 W</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Lado del telar: limita la corriente si hay un error de cableado</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Entre el + del conector de cada lector y el pin 4 de su LCA110</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>De 470 Ω 3 W porque el lector del C 201 se alimenta con 15 a 30 V (medido el 17/10/2026); con hasta 15 V sería de 220 Ω 2 W. Del lado del telar: nunca al GND del ESP32.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="7">
-      <c r="A28" s="10" t="n">
+    <row r="28" ht="25" customHeight="1" s="7">
+      <c r="A28" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Resistencia 10 kΩ 1/2 W (lado del telar)</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Deja la señal en 0 V (papel) con el relé abierto</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Entre la señal y el − del conector de cada lector</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>Del lado del telar: nunca al GND del ESP32.</t>
         </is>
@@ -1177,29 +1186,29 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="7">
-      <c r="A31" s="10" t="n">
+    <row r="31" ht="25" customHeight="1" s="7">
+      <c r="A31" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Gabinete IP65 + prensacables</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Protege el nodo del polvo y la pelusa textil</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>Montado en pared o columna, no sobre el chasis del telar.</t>
         </is>
@@ -1233,29 +1242,29 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60.5" customHeight="1" s="7">
-      <c r="A33" s="10" t="n">
+    <row r="33" ht="69" customHeight="1" s="7">
+      <c r="A33" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Cable multifilar 6 conductores, 1 mm²</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Lleva la señal de los 3 botones hasta el gabinete: el mismo par sirve para el relé y para el sensado</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Un par por botón, del telar a las borneras del gabinete</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Sin blindaje. Se descartó el cable mallado tras consulta profesional: la señal de contacto seco a 24 V tiene inmunidad de sobra, el telar no tiene variador de frecuencia y su electrónica está en una caja metálica que contiene el ruido. Único recaudo: no correrlo pegado y en paralelo al cable del motor.</t>
         </is>

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -860,7 +860,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Capacitor electrolítico 470 µF (220 a 470 µF) 16 V o más</t>
+          <t>Capacitor electrolítico 470 µF, 16 V o más</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>3 en los relés + 3 en el sensado</t>
+          <t>3 en los relés + 1 en el sensado (GPIO 34)</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>5 van a 3V3 y la de GPIO 27 va a GND (módulo activo-alto).</t>
+          <t>3 van a 3V3 (GPIO 25, 26 y 34) y la de GPIO 27 va a GND (módulo activo-alto). GPIO 32 y 33 usan la pull-up interna del ESP32.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Componentes_en_placa.xlsx
+++ b/documentacion_proyecto/Componentes_en_placa.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="6" min="1" max="1"/>
@@ -1158,21 +1158,21 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="9" t="n"/>
     </row>
-    <row r="30" ht="88" customHeight="1" s="7">
+    <row r="30" ht="100" customHeight="1" s="7">
       <c r="A30" s="10" t="n">
         <v>23</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Placa universal perforada</t>
+          <t>Plaquetas (placas de circuito)</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Soporte definitivo del circuito (reemplaza la protoboard): la de la fuente, la principal (ESP32), la de los módulos de relé y la del Nivel 2 (Bloques C y D, sumada el 10/10/2026, con todo ya probado en protoboard). El sensado de la botonera va en su propia plaqueta impresa (diseñada en Proteus), unida a la principal por J4</t>
+          <t>Soporte definitivo del circuito (reemplaza la protoboard): la de la fuente, la principal (en Proteus, plaqueta 2 parte 1), la de los módulos de relé (2 parte 2), la del Nivel 2 (plaqueta 3), la del sensado de la botonera (info B) y, desde el 25/10/2026, la plaqueta del ESP32. Las diseñadas en Proteus son impresas</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión.</t>
+          <t>La entrega final va soldada, no sobre protoboard. La fuente va aparte: lo que lleva 220 V queda separado de la baja tensión. En la principal impresa faltaron dos pistas y en la del Nivel 2 una: van con puentes de alambre (n.º 32).</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1" s="7">
+    <row r="35" ht="62" customHeight="1" s="7">
       <c r="A35" s="10" t="n">
         <v>28</v>
       </c>
@@ -1322,7 +1322,119 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Se suman el 10/10/2026. Permiten sacar módulos y cables sin desoldar.</t>
+          <t>Se suman el 10/10/2026. Permiten sacar módulos y cables sin desoldar. En la principal, J5, J6 y J7 no llevan tira: ahí se sueldan los cables que vienen de la plaqueta del ESP32.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="62" customHeight="1" s="7">
+      <c r="A36" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Plaqueta del ESP32: tiras hembra de 19 pines</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Zócalo del ESP32 de 38 pines, en el orden correcto (pin 1 del lado de la antena)</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Las dos tiras a 25,4 mm. Salidas: P1 (3V3, IO34, IO35, IO32, IO33, IO25, IO26, IO27, GND, 5V) y P2 (IO22, IO21, GND, IO19, IO18)</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Se suma el 25/10/2026: en la principal impresa la tira derecha del ESP32 quedó con J5 y J7 invertidos y el ESP32 no se puede enchufar ahí. Medir el módulo antes de soldar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="100" customHeight="1" s="7">
+      <c r="A37" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Plaqueta del ESP32: tiras macho P1 (10 pines) y P2 (5 pines)</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Salidas de las señales del ESP32 hacia la principal</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>P1-1 3V3 → J5-1 · P1-2 IO34 → J5-5 · P1-3 IO35 → J5-6 · P1-4 IO32 → J5-7 · P1-5 IO33 → J5-8 · P1-6 IO25 → J5-9 · P1-7 IO26 → J7-1 · P1-8 IO27 → J7-2 · P1-9 GND → J7-5 · P1-10 5V → J7-10 · P2-1 IO22 → J6-3 · P2-2 IO21 → J6-6 · P2-3 GND → J6-7 · P2-4 IO19 → J6-8 · P2-5 IO18 → J6-9</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Cada cable va al pad que tiene esa señal en la principal, no a la posición: así el orden invertido de J5 y J7 deja de importar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="62" customHeight="1" s="7">
+      <c r="A38" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Cables dupont hembra (de P1 y P2 a la principal)</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Unen la plaqueta del ESP32 con la principal</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Hembra en P1/P2; el otro extremo soldado al pad de la principal (tabla de la fila anterior)</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Colores fijos: rojo 5V, naranja 3V3, negro GND. Antes de enchufar el ESP32: continuidad de cada cable y 5 V entre P1-10 y P1-9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="62" customHeight="1" s="7">
+      <c r="A39" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Puentes de alambre aislado</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Reemplazan las pistas que faltaron en las plaquetas impresas</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Principal: J4-3 ↔ J5-5 (GPIO 34) y J8-1 ↔ J5-6 (GPIO 35). Nivel 2: U3 ↔ R7 (GPIO 19)</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Soldados del lado del cobre, lo más cortos posible, sin pasar sobre otro pad. Medir continuidad de punta a punta y que no toquen las patas de al lado.</t>
         </is>
       </c>
     </row>
